--- a/output/nbo_review_required.xlsx
+++ b/output/nbo_review_required.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Use MASTER_DATASET as the base training table. Blank cells indicate attributes not explicitly identified in the source batch.</t>
+          <t>Use MASTER_DATASET as the base training table. Blank cells indicate attributes that could not be safely extracted or inferred.</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>BNK/IBG are inferred from the product family and source folder. Re-run export to upsert matching products.</t>
+          <t>BNK/IBG are inferred from the product family and source folder. Compact inferred values are used when the document strongly implies a field.</t>
         </is>
       </c>
     </row>
@@ -575,14 +575,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -592,11 +592,11 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
@@ -608,7 +608,7 @@
     <col width="18" customWidth="1" min="28" max="28"/>
     <col width="19" customWidth="1" min="29" max="29"/>
     <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="18" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -620,7 +620,7 @@
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
-    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="42" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,27 +843,27 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Zaamin Takaful Plan</t>
+          <t>Home Loans</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>IBG</t>
+          <t>BNK</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Banca Takaful</t>
+          <t>SBP Covid 19 Schemes</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>SBP Schemes Covid-19 Annexure C</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>SBP Schemes Covid-19 Annexure C</t>
         </is>
       </c>
       <c r="F2" s="3" t="n"/>
@@ -871,39 +871,45 @@
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>60</v>
-      </c>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Alfalah Insurance Zaamin Takaful Plan</t>
+          <t>SBP Schemes Covid-19 Annexure C</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Debit Card</t>
+          <t>SBP Schemes Covid-19 Annexure C</t>
         </is>
       </c>
       <c r="Q2" s="3" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
-      <c r="U2" s="3" t="n"/>
-      <c r="V2" s="3" t="n"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="3" t="n"/>
-      <c r="AC2" s="3" t="n"/>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>0-50 Mn</t>
+        </is>
+      </c>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="3" t="n"/>
@@ -917,7 +923,229 @@
       <c r="AN2" s="3" t="n"/>
       <c r="AO2" s="3" t="n"/>
       <c r="AP2" s="3" t="n"/>
-      <c r="AQ2" s="3" t="n"/>
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <t>Product Head- Secured Business Head-secured Segment Head Of Credit Operations Head Of Credit Risk Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>SBP Financial Relief</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>BNK</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>SBP Covid 19 Schemes</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Deferral</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Finance Relief</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Salaried</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Salaried</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Salaried</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 SBP Financial Relief Consumers</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 SBP Financial Relief Consumers</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Open To All</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Financial Relief</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="5" t="n"/>
+      <c r="X3" s="5" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="5" t="n"/>
+      <c r="AC3" s="5" t="n"/>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Products</t>
+        </is>
+      </c>
+      <c r="AF3" s="5" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="inlineStr">
+        <is>
+          <t>1 Y</t>
+        </is>
+      </c>
+      <c r="AI3" s="5" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="AJ3" s="5" t="n"/>
+      <c r="AK3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="5" t="n"/>
+      <c r="AM3" s="5" t="n"/>
+      <c r="AN3" s="5" t="n"/>
+      <c r="AO3" s="5" t="n"/>
+      <c r="AP3" s="5" t="n"/>
+      <c r="AQ3" s="5" t="inlineStr">
+        <is>
+          <t>Deferral Up To 1 Year; Rescheduling Up To 2 Years</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 Annexure B</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>BNK</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SBP Covid 19 Schemes</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 Annexure B</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 Annexure B</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 Annexure B</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>SBP Schemes Covid-19 Annexure B</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>SBS</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>Markup</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>3 Y</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" s="3" t="n"/>
+      <c r="AM4" s="3" t="n"/>
+      <c r="AN4" s="3" t="n"/>
+      <c r="AO4" s="3" t="n"/>
+      <c r="AP4" s="3" t="n"/>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>0% Markup, Extend Tenure Up To 3 Years</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AQ1"/>
